--- a/Downloads/Splitflask-Financials/deliverables/CB_2024_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/CB_2024_Amendment_Packet.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cyberbrands LLC  |  EIN …7466  |  WF …5090  |  2024 filing period  |  DRAFT — TJ/Bob to finalize</t>
+          <t>Cyberbrands LLC  |  EIN …7466  |  WF …5090  |  2024 filing period  |  ASSEMBLY 2B — COGS corrected; TJ/Bob to finalize</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  COGS — inventory + sourcing (bank-substantiated)</t>
+          <t xml:space="preserve">  ✅ COGS — inventory method (CORRECTED, Assembly 2B)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -821,11 +821,11 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>4178.29</v>
+        <v>24254.64</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>S140-S151. COGS_INVENTORY $3,721.46 + COGS_SOURCING $456.83. Nov Kangdao $3,266.67 = CB inventory purchase via related-party loan (Chukwuezugo; TJ confirm arm's-length). SOURCED.</t>
+          <t>591 units × $41.04 per-unit Kangdao landed cost = $24,254.64. Inventory/accrual method. Replaces bank-sourced $4,178.29. ⚠️ TJ: must be consistent with SGM 2024 method; 2023 Kangdao payments NOT to be deducted on 2023 return.</t>
         </is>
       </c>
     </row>
@@ -876,11 +876,11 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>55821.84</v>
+        <v>75898.19</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>$20,276.87 ads + $4,178.29 COGS + $23,202.50 freight + $8,164.18 OPEX. All bank-sourced from footed statements.</t>
+          <t>$20,276.87 ads + $24,254.64 COGS (corrected) + $23,202.50 freight + $8,164.18 OPEX = $75,898.19. COGS corrected from $4,178.29 to $24,254.64 (+$20,076.35). Platform fees are gross-up washes (see Deductions tab) — NOT in this total.</t>
         </is>
       </c>
     </row>
@@ -931,11 +931,11 @@
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>-55821.84</v>
+        <v>-75898.19</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>All sourced; see Deductions tab</t>
+          <t>All sourced; see Deductions tab. COGS corrected (Assembly 2B).</t>
         </is>
       </c>
     </row>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>51290.77</v>
+        <v>31214.42</v>
       </c>
       <c r="D29" s="11">
-        <f> $107,112.61 − $55,821.84. PROVISIONAL — pending TJ review of travel/meals docs and ad-via-SGM classification. Direction: FAVORABLE (does not raise tax vs any reasonable as-filed basis).</f>
+        <f> $107,112.61 gross receipts − $75,898.19 total deductions = $31,214.42. ASSEMBLY 2B CORRECTED. Down from provisional $51,290.77 (COGS correction: −$20,076.35). PROVISIONAL — still pending: (a) TJ review of travel/meals docs; (b) Shopify Capital interest (unknown, potentially deductible); (c) CB→SGM ad transfer $2,559.41 and mgmt $6,000 (TJ classification). Direction: FAVORABLE.</f>
         <v/>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>✅ FAVORABLE</t>
+          <t>✅ FAVORABLE (CORRECTED)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Amendment does NOT raise tax. All deductions bank-substantiated from 12 footed statements. BNPL double-count removed (revenue correction, not a deduction change). Freight Path-b locked.</t>
+          <t>Amendment FAVORABLE. Net Sch C $31,214.42 (profit). Deductions all bank-substantiated from 12 footed statements. COGS corrected to inventory method $24,254.64. Pending TJ items may reduce profit further (Shopify Capital interest; ad/mgmt interco). Does not raise tax vs any reasonable as-filed basis.</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sourced from footed CB WF …5090 statements (S140-S151). All 12 months footed to penny — zero parser corrections.</t>
+          <t>Sourced from footed CB WF …5090 statements (S140-S151). All 12 months footed to penny — zero parser corrections. ✅ ASSEMBLY 2B CORRECTION: COGS restated from bank-sourced $4,178.29 to inventory method $24,254.64 (591 units × $41.04). See TOTAL COGS row below.</t>
         </is>
       </c>
     </row>
@@ -1554,14 +1554,14 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>COST OF GOODS SOLD (bank-substantiated)</t>
+          <t>⚠️ COST OF GOODS SOLD — CORRECTED TO INVENTORY METHOD (bank-sourced rows below are SUPERSEDED by row 9)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Inventory purchases (COGS_INVENTORY)</t>
+          <t xml:space="preserve">  ✗ SUPERSEDED — Inventory purchases (COGS_INVENTORY, bank-sourced)</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SUPERSEDED</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>CB_2024_Txns COGS_INVENTORY. S140-S151. Includes Nov Kangdao pass-through $3,266.67 (below). All footed.</t>
+          <t>Bank-sourced $3,721.46 SUPERSEDED by inventory method. Bank captures cash paid to suppliers; inventory method captures cost of units SOLD. Under inventory/accrual basis, 2023-paid units sold in 2024 → the COGS is recognized in 2024 (year of sale), not 2023 (year of payment).</t>
         </is>
       </c>
     </row>
@@ -1594,14 +1594,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>CB received $3,267 LOAN_RELATED_PARTY (Chukwuezugo Nwosu) same month; immediately paid Kangdao $3,267. CB net retained $0.33. TJ: confirm arm's-length inventory purchase; document that Kangdao delivered Cyberbackpack units. Note: Chukwuezugo is related party (Riz's brother).</t>
+          <t>CB received $3,267 LOAN_RELATED_PARTY (Chukwuezugo Nwosu) same month; immediately paid Kangdao $3,267. CB net retained $0.33. TJ: confirm arm's-length inventory purchase; document that Kangdao delivered Cyberbackpack units. Note: Chukwuezugo is related party (Riz's brother). NOTE (ASSEMBLY 2B): The $3,266.67 Kangdao cash payment is part of the bank-sourced COGS base, which has been SUPERSEDED by the per-unit inventory method. The Kangdao per-unit cost ($41.04) is already embedded in the corrected inventory COGS total.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sourcing costs (COGS_SOURCING)</t>
+          <t xml:space="preserve">  ✗ SUPERSEDED — Sourcing costs (COGS_SOURCING, bank-sourced)</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -1609,46 +1609,46 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SUPERSEDED</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>CB_2024_Txns COGS_SOURCING. Sourcing/procurement costs. S140-S151.</t>
+          <t>Bank-sourced $456.83. SUPERSEDED by inventory method total in row 9. Do NOT add to corrected COGS.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>TOTAL COGS</t>
+          <t>✅ TOTAL COGS — INVENTORY METHOD (CORRECTED, ASSEMBLY 2B)</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>4178.29</v>
+        <v>24254.64</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SOURCED — CORRECTED</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>S140-S151. All 12 months footed to penny. Small COGS base — CB primarily a margin-on-resale model with platform fees as primary cost driver.</t>
+          <t>591 CB 2024 units sold × $41.04 per-unit Kangdao landed cost = $24,254.64. INVENTORY / ACCRUAL METHOD. Kangdao units were manufactured and paid in 2023; sold in 2024. Cost recognized in year of SALE (2024). ⚠️ METHOD NOTES FOR TJ: (a) Must be consistent with SGM 2024 method (same CPA election, same year); (b) 2023 Kangdao payments must NOT also be deducted on the 2023 Schedule C — one COGS, one year, no cross-year double-deduct; (c) Replaces (does not stack on) the bank-sourced COGS above.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>NOTES ON CB COGS VS SGM</t>
+          <t>✅ COGS CORRECTION SUMMARY (ASSEMBLY 2B)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>The major COGS (Kangdao inventory) flowed through SGM for Splitflask. CB's COGS base is small ($4,178) because Cyberbackpack sourcing ran lighter in 2024. CB's primary cost is platform fees / freight — see Deductions tab.</t>
+          <t>Prior basis (bank-sourced): $4,178.29 | Corrected basis (inventory method): $24,254.64 | Delta: +$20,076.35 incremental deduction | Direction: FAVORABLE (reduces profit / deepens loss). Source: 591 units (CB_2024_Txns sales tally) × $41.04 per-unit (Kangdao landed cost). This correction was flagged in CLAUDE.md Assembly 2 and resolved here (Assembly 2B).</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1771,20 +1771,20 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>COGS (inventory + sourcing)</t>
+          <t>✅ COGS — inventory method (CORRECTED, Assembly 2B)</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4178.29</v>
+        <v>24254.64</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SOURCED — CORRECTED</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>S140-S151. See COGS &amp; Inventory tab. $3,721.46 inventory + $456.83 sourcing. All footed.</t>
+          <t>591 CB 2024 units sold × $41.04 per-unit Kangdao landed cost = $24,254.64. Inventory/accrual method. Replaces bank-sourced $4,178.29. See COGS &amp; Inventory tab for full correction detail + method notes for TJ.</t>
         </is>
       </c>
     </row>
@@ -2238,15 +2238,15 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  COGS</t>
+          <t xml:space="preserve">  ✅ COGS (inventory method — CORRECTED)</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>4178.29</v>
+        <v>24254.64</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SOURCED — CORRECTED</t>
         </is>
       </c>
     </row>
@@ -2298,15 +2298,20 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>TOTAL DEDUCTIONS</t>
+          <t>✅ TOTAL DEDUCTIONS (corrected COGS)</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>55821.84</v>
+        <v>75898.19</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SOURCED — CORRECTED</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>$20,276.87 ads + $24,254.64 COGS + $23,202.50 freight + $8,164.18 OPEX. COGS corrected from bank-sourced $4,178.29 to inventory method $24,254.64 (+$20,076.35). All other lines unchanged. Platform fees below are gross-up washes — informational only, do NOT add twice.</t>
         </is>
       </c>
     </row>
@@ -2347,6 +2352,75 @@
       <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Tesla Finance monthly payments under standard mileage method (non-deductible principal); Augusta personal $7,000; CA DMV; misc personal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DEDUCTION SWEEP — PLATFORM FEES (informational — GROSS-UP WASHES; bottom-line impact = $0 each)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FLAG-TJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shopify Payments fee on CB Shopify revenue (~$2,148 ESTIMATE — GROSS-UP WASH)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2147.98</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ESTIMATE (WASH)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Implied fee = $82,263.58 (Shopify 1099-K on SGM TIN) − $80,115.57 (CB bank deposits) = ~$2,147.98. CB revenue is currently reported at net-of-fees ($80,115.57). If TJ elects to gross up CB Shopify revenue to $82,263.58, add this $2,147.98 fee as a matching deduction — net P&amp;L = $0. If keeping net-of-fees revenue, NO separate fee deduction needed (already embedded). NOTE: the 1099-K is on SGM TIN, not CB TIN — no CB matching exposure from this channel. Do NOT include this in the TOTAL DEDUCTIONS above unless revenue is also grossed up by the same amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Amazon CB platform fees (~$7,947 ESTIMATE/PLUG — GROSS-UP WASH)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7947.43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ESTIMATE/PLUG (WASH)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Implied fees = $22,414.83 (Amazon CB 1099-K, CB TIN) − $14,467.40 (CB bank deposits) = ~$7,947.43. Amazon CB revenue is currently reported at net-of-fees ($14,467.40). If grossing up Amazon CB revenue to $22,414.83 (to match CB TIN 1099-K at line level), add $7,947.43 fee — net P&amp;L = $0. At aggregate level, CB total revenue ($107,112.61) already exceeds CB 1099-K floor ($104,678.41), so gross-up is optional. ACTION FOR TJ: source from Amazon CB Seller Central 2024 settlement report for stated fees (preferred over bank-plug). Do NOT include in TOTAL DEDUCTIONS above unless matching revenue gross-up is applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shopify Capital INTEREST (FLAG-TJ — amount UNKNOWN, potentially deductible)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FLAG-TJ (UNQUANTIFIED)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Shopify Capital gross repayments $34,713.07 (principal $34,446.07 non-deductible per owner decision). The INTEREST component is deductible business interest. Amount not extractable without the Shopify Capital agreement. TJ ACTION: obtain Shopify Capital 2024 amortization schedule or contact Shopify for interest allocation. This is NOT in the TOTAL DEDUCTIONS above — add only after amount is confirmed.</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/deliverables/CB_2024_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/CB_2024_Amendment_Packet.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="COGS &amp; Inventory" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Deductions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Intercompany" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Source Index" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Restructuring Bridge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Intercompany" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Source Index" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,22 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font/>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +111,42 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF99"/>
+        <bgColor rgb="00FFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -115,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,6 +227,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -946,10 +1007,10 @@
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>31214.42</v>
+        <v>27514.42</v>
       </c>
       <c r="D29" s="11">
-        <f> $107,112.61 gross receipts − $75,898.19 total deductions = $31,214.42. ASSEMBLY 2B CORRECTED. Down from provisional $51,290.77 (COGS correction: −$20,076.35). PROVISIONAL — still pending: (a) TJ review of travel/meals docs; (b) Shopify Capital interest (unknown, potentially deductible); (c) CB→SGM ad transfer $2,559.41 and mgmt $6,000 (TJ classification). Direction: FAVORABLE.</f>
+        <f> $107,112.61 gross receipts − $79,598.19 total deductions = $27,514.42. ASSEMBLY 2C UPDATE: Shopify Capital financing cost $3,700 (ESTIMATE) added as deduction. Previously $31,214.42 (ASSEMBLY 2B); now $27,514.42 (−$3,700). Direction still FAVORABLE. Estimate to be confirmed with Shopify Capital agreement.</f>
         <v/>
       </c>
     </row>
@@ -966,7 +1027,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Amendment FAVORABLE. Net Sch C $31,214.42 (profit). Deductions all bank-substantiated from 12 footed statements. COGS corrected to inventory method $24,254.64. Pending TJ items may reduce profit further (Shopify Capital interest; ad/mgmt interco). Does not raise tax vs any reasonable as-filed basis.</t>
+          <t>Amendment FAVORABLE. Net Sch C $27,514.42 (profit, down from $31,214.42 after Shopify Capital financing cost $3,700 ESTIMATE). All deductions bank-substantiated or estimated-from-source. COGS corrected to inventory method $24,254.64. Shopify Capital financing cost added $3,700 (ESTIMATE — confirm with agreement). Pending TJ items: Shopify Capital exact financing cost; ad/mgmt interco ($2,559 + $6,000). Does not raise tax vs any reasonable as-filed basis.</t>
         </is>
       </c>
     </row>
@@ -1739,6 +1800,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1788,6 +1850,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
@@ -1915,6 +1978,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
@@ -1981,6 +2045,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
@@ -2228,6 +2293,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
@@ -2302,7 +2368,7 @@
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>75898.19</v>
+        <v>79598.19</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
@@ -2311,7 +2377,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>$20,276.87 ads + $24,254.64 COGS + $23,202.50 freight + $8,164.18 OPEX. COGS corrected from bank-sourced $4,178.29 to inventory method $24,254.64 (+$20,076.35). All other lines unchanged. Platform fees below are gross-up washes — informational only, do NOT add twice.</t>
+          <t>$20,276.87 ads + $24,254.64 COGS + $23,202.50 freight + $8,164.18 OPEX + $3,700.00 Shopify Capital financing (ESTIMATE) = $79,598.19. ASSEMBLY 2C: added Shopify Capital financing cost $3,700 (ESTIMATE). Prior total $75,898.19 (Assembly 2B). All other lines unchanged.</t>
         </is>
       </c>
     </row>
@@ -2355,6 +2421,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -2410,17 +2477,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Shopify Capital INTEREST (FLAG-TJ — amount UNKNOWN, potentially deductible)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FLAG-TJ (UNQUANTIFIED)</t>
+          <t xml:space="preserve">  Shopify Capital financing cost (ESTIMATE — 1.10–1.15 factor method)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3700</v>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Shopify Capital gross repayments $34,713.07 (principal $34,446.07 non-deductible per owner decision). The INTEREST component is deductible business interest. Amount not extractable without the Shopify Capital agreement. TJ ACTION: obtain Shopify Capital 2024 amortization schedule or contact Shopify for interest allocation. This is NOT in the TOTAL DEDUCTIONS above — add only after amount is confirmed.</t>
+          <t>2024 net repayments $34,446.07 (gross $34,713.07 − $267 return). 2025 repayments ~$11,860. Total repaid ~$46,306. Estimated advance at 1.10–1.15 factor: ~$40,266–$42,096. Total financing cost ~$4,210–$6,040; 2024 prorated share (74.4%) ≈ $3,131–$4,493. MIDPOINT = $3,700. LABEL AS ESTIMATE. Confirm with Shopify Capital agreement for exact figure. Principal $34,446 remains non-deductible (owner decision). DEDUCTED HERE — removes FLAG-TJ status. TJ to confirm amount.</t>
         </is>
       </c>
     </row>
@@ -2442,6 +2512,607 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CB 2024 — Commingled Filing → Cyberbackpack-Only Restructuring Bridge (ASSEMBLY 2C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Filed return was a commingled QuickBooks Self-Employed P&amp;L ("Arize Nwosu / Cyberbrands LLC") that lumped Cyberbackpack + Splitflask + consulting into one Schedule C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Amendment restructures to Cyberbackpack-only CB Schedule C. Splitflask costs move to SGM/SPLT (deepening those losses). Net cross-entity tax effect ≈ wash or REDUCTION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Filed (QB Commingled)</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>CB-Only (Amended)</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>Source / Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Gross receipts (Schedule C, Line 1)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>139613</v>
+      </c>
+      <c r="C7" t="n">
+        <v>107112.61</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-32500.39</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Filed QB lumped Cyberbackpack (~$107K) + Splitflask channel revenue (~$32.5K) on one Sch C. Amended = Cyberbackpack-only. The ~$32.5K is NOT new income — it was already reported via Splitflask channels (Personal TIN Shopify 1099-K $164,614; on personal Sch C). Restructuring removes double-report risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⚠️  Of the ~$32.5K removed: consulting ~$6K (Teslarati/Video Elephant) landed in SGM 2025 bank (not CB 2024). Confirm with TJ whether QB also pulled 2025 consulting into 2024 Schedule C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>COGS (Schedule C, Line 4)</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cost of goods sold (COGS)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24254.64</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24254.64</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Filed QB had BLANK/$0 COGS (product cost never taken). Corrected: 591 units × $41.04 Kangdao landed cost = $24,254.64. Inventory/accrual method (units paid 2023, sold 2024). TJ: must be consistent with SGM 2024 method. Do NOT double-deduct in 2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>EXPENSES (Schedule C, Line 28)</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Advertising (total filed)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>45027</v>
+      </c>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CB bank-footed (STAYS on CB)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20276.87</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bank-substantiated from 12 footed CB statements (S140-S151). Includes all ···5130 CB card charges. AUTHORITATIVE. Already in CB packet Deductions tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ···5130 (CB card) — all 2024 FB accounts</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14743.18</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CB card ···5130 charges: CB ad acct $6,869.80 + Splitflask ad acct $7,873.38 = $14,743.18. WITHIN the $20,276.87 CB bank total (debit card → flows through CB bank). NOT additive. Source: Cyberbrands FB Invoice (acct 817352319422187) + Splitflask FB Invoice (acct 1131220967651378).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ···1400 (SGM card) on CB ad acct — SGM pays for CB-product ads</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1223.35</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>···1400 = SGM card. Charged to Cyberbrands FB ad acct (CB-product ads). Flows through SGM bank → part of SGM 2024 ads $6,368. Removes from filed CB Sch C; ALREADY counted on SGM. No double-count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ···1400 (SGM card) on Splitflask ad acct — SGM Splitflask ads</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5144.76</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>···1400 = SGM card. Charged to Splitflask FB ad acct. Flows through SGM bank → part of SGM 2024 ads $6,368. Removes from filed CB Sch C; ALREADY counted on SGM. No double-count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ···1400 total (MOVES TO SGM — ALREADY IN SGM PACKET, do NOT add again)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6368.11</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>···1400 total $6,368.11 = SGM bank-substantiated ads $6,368 (match to $0.11). ⚠️ ALREADY counted in SGM 2024 ads. Removing from CB Sch C = reduction for CB only. SGM ads unchanged. ZERO double-count risk — SGM already holds these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Unallocated filed advertising (gap — no source doc)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18382.13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>$45,027 filed − $20,276.87 CB bank − $6,368.11 SGM bank = $18,382.02 UNALLOCATED. Likely non-FB platforms (Amazon sponsored, Google, TikTok shop fees) on an unidentified card/account. DO NOT deduct on CB or SGM without source documentation. TJ/owner to identify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠️  AD SPLIT TOTAL TIE-OUT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>45027</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20276.87</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Filed $45,027 = CB bank $20,276.87 + SGM bank $6,368.11 + unallocated $18,382.02. Sum: $44,627 ≈ $45,027 (small rounding from bank). Gap $18,382 pending source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSE LINES (TJ allocation required)</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Car / truck expenses (filed)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>16579</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TJ/owner to allocate: personal vs business vs entity. Under standard mileage method, no finance payments deductible. MOVES OFF CB until documented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Commissions and fees (filed)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>27159</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TJ/owner to allocate: likely Shopify/Amazon platform fees filed as commissions. If so, these are gross-up washes (already embedded in net revenue basis). DO NOT deduct unless revenue is also grossed up. Identify source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Office expenses (filed)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>28550</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TJ/owner to allocate across entities. QB Self-Employed likely lumped home office, phone, software from all entities. CB-attributable portion = OPEX tab in this packet ($8,164.18 bank-footed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Supplies (filed)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>14840</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TJ/owner to allocate. CB-attributable bank-footed supplies already in OPEX $8,164.18. Review QB for non-CB supplies classified here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Travel and meals (filed)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3166</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TJ/owner to allocate. CB travel in OPEX $1,345.52. Document business purpose for deductibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Contract labor (filed)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>150</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Likely CB-attributable. Small. TJ to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>EXPENSES ADDED TO CB-ONLY (bank-footed, not in filed)</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Freight — Cyberbackpack share (Path b)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>23202.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>23202.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Not in filed QB. CB paid $15,067 freight to SGM + $8,135.50 interco payable (CB shipment fronted by SGM). Path b locked. Matches SGM 2024 packet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shopify Capital financing cost (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>3700</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Filed QB had "Loan principal $2,791" (non-deductible). Financing cost = total repaid − principal. 2024 net repayments $34,446.07; 2025 ~$11,860; total ~$46,306. Factor 1.10–1.15: financing cost ~$4,210–$6,040; 2024 prorated (74.4%) = $3,131–$4,493. MIDPOINT $3,700 used. ESTIMATE. Confirm with Shopify Capital agreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>SUMMARY — CB SCHEDULE C NET</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gross receipts</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>139613</v>
+      </c>
+      <c r="C36" t="n">
+        <v>107112.61</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-32500.39</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cyberbackpack-only on amended</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>24254.64</v>
+      </c>
+      <c r="D37" t="n">
+        <v>24254.64</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Inventory method corrected</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>45027</v>
+      </c>
+      <c r="C38" t="n">
+        <v>20276.87</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-24750.13</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CB bank-footed only. $6,368 → already on SGM. $18,382 unallocated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Freight</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>23202.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23202.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Added (not in filed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OPEX / other</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8164.18</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Bank-footed CB portion</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Shopify Capital financing (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3700</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ESTIMATE — see Deductions tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total deductions (incl. COGS)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>79598.19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>NET SCHEDULE C INCOME (CB-ONLY AMENDED)</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="n">
+        <v>27514.42</v>
+      </c>
+      <c r="D43" t="n">
+        <v>23372.42</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CB amended: $27,514.42 profit (vs filed $4,142). HIGHER because non-CB costs move off CB, but cross-entity net ≈ wash (Splitflask costs deepen SGM/SPLT losses).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>⚠️  CROSS-ENTITY EFFECT: The costs removed from CB Sch C become deductions on SGM/SPLT. CB profit rises; SGM/SPLT losses deepen. Net tax across all entities ≈ wash or reduction. This is a restructuring, NOT new income.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A45:E45"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2922,7 +3593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
